--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elmichvietnam-my.sharepoint.com/personal/hoang_bui_elmich_vn/Documents/Documents/UiPath/GiaoHangNhanh/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RPA\live\ghn_vnpay_ghtk\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{00D541BD-CB78-4D75-8532-9AD73E8C785E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2120C47-4F6E-4476-B67E-43A476D18817}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6774324F-FF4D-4420-89B3-C8762056810E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
     <x:workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
@@ -104,15 +104,12 @@
     <x:t>VNPAY_user</x:t>
   </x:si>
   <x:si>
-    <x:t>0852843351</x:t>
+    <x:t>0903487692</x:t>
   </x:si>
   <x:si>
     <x:t>VNPAY_Password</x:t>
   </x:si>
   <x:si>
-    <x:t>ICTElmich@123456</x:t>
-  </x:si>
-  <x:si>
     <x:t>VNPAY_transactions</x:t>
   </x:si>
   <x:si>
@@ -137,10 +134,16 @@
     <x:t>Elmich123@@</x:t>
   </x:si>
   <x:si>
+    <x:t>DayOfWeek</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WED</x:t>
+  </x:si>
+  <x:si>
     <x:t>fileNewest</x:t>
   </x:si>
   <x:si>
-    <x:t/>
+    <x:t>,GHN_Phien_Chuyen_Tien_30_03_2026_COD_202603300313_2631581.xlsx,GHN_Phien_Chuyen_Tien_27_03_2026_COD_202603270400_2631581.xlsx,GHN_Phien_Chuyen_Tien_26_03_2026_COD_202603260314_2631581.xlsx,GHN_Phien_Chuyen_Tien_25_03_2026_COD_202603250402_2631581.xlsx,GHN_Phien_Chuyen_Tien_24_03_2026_COD_202603240407_2631581.xlsx,GHN_Phien_Chuyen_Tien_23_03_2026_COD_202603230313_2631581.xlsx</x:t>
   </x:si>
   <x:si>
     <x:t>Asset</x:t>
@@ -222,7 +225,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -235,7 +238,6 @@
     </x:xf>
     <x:xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <x:xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -262,9 +264,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -302,7 +304,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -408,7 +410,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -550,7 +552,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -631,10 +633,10 @@
     </x:row>
     <x:row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <x:row r="7" spans="1:26" ht="14.25" customHeight="1">
-      <x:c r="A7" s="10" t="s">
+      <x:c r="A7" s="9" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B7" s="11"/>
+      <x:c r="B7" s="10"/>
     </x:row>
     <x:row r="8" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A8" s="0" t="s">
@@ -705,44 +707,51 @@
       <x:c r="A17" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B17" s="3" t="s">
-        <x:v>25</x:v>
+      <x:c r="B17" s="0" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A18" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B18" s="3" t="s">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:26" ht="14.25" customHeight="1"/>
     <x:row r="20" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A20" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B20" s="3" t="s">
-        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A21" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="B21" s="9" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:26" ht="14.25" customHeight="1">
       <x:c r="A22" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B22" s="3" t="s">
+    </x:row>
+    <x:row r="23" spans="1:26" ht="14.25" customHeight="1">
+      <x:c r="A23" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
+      <x:c r="B23" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
     </x:row>
-    <x:row r="23" ht="14.25" customHeight="1"/>
     <x:row r="24" ht="14.25" customHeight="1"/>
     <x:row r="25" ht="14.25" customHeight="1"/>
     <x:row r="26" ht="14.25" customHeight="1"/>
@@ -1774,10 +1783,10 @@
     </x:row>
     <x:row r="2" spans="1:26" ht="14.5" customHeight="1">
       <x:c r="A2" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C2" s="2"/>
     </x:row>
@@ -2800,13 +2809,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E1" s="1"/>
       <x:c r="F1" s="1"/>
